--- a/Outputs/Scenarios/PtX_demand_DE_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DE_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.02207968662960989</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009835277510041367</v>
+        <v>0.01269466743197721</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01639212918340228</v>
+        <v>0.01406271365437914</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>0.0003181309096915025</v>
       </c>
       <c r="K28" t="n">
-        <v>0.006556851673360911</v>
+        <v>0.006026877280448203</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.03268628793279557</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05240804800331546</v>
+        <v>0.06764453158357187</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08734674667219244</v>
+        <v>0.07493427323256913</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.001720330943831346</v>
       </c>
       <c r="K42" t="n">
-        <v>0.03493869866887698</v>
+        <v>0.03211468852824391</v>
       </c>
     </row>
     <row r="43">
